--- a/tests/worked_examples/staged/three_stages_with_loans_and_a_staged_grant.xlsx
+++ b/tests/worked_examples/staged/three_stages_with_loans_and_a_staged_grant.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-19</t>
+          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -520,6 +520,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -877,6 +878,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -891,7 +893,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>70328.54125171698</v>
+        <v>60648.43755924105</v>
       </c>
       <c r="C44" t="n">
         <v>0.01</v>
@@ -909,7 +911,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4727.182664489051</v>
+        <v>4076.527645188313</v>
       </c>
       <c r="C45" t="n">
         <v>0.01</v>
@@ -945,7 +947,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24827.80052146591</v>
+        <v>15147.69682898998</v>
       </c>
       <c r="C47" t="n">
         <v>0.01</v>

--- a/tests/worked_examples/staged/three_stages_with_loans_and_a_staged_grant.xlsx
+++ b/tests/worked_examples/staged/three_stages_with_loans_and_a_staged_grant.xlsx
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>60648.43755924105</v>
+        <v>64641.02342882127</v>
       </c>
       <c r="C44" t="n">
         <v>0.01</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4076.527645188313</v>
+        <v>4344.892129553368</v>
       </c>
       <c r="C45" t="n">
         <v>0.01</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15147.69682898998</v>
+        <v>19140.2826985702</v>
       </c>
       <c r="C47" t="n">
         <v>0.01</v>
